--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -135,7 +135,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
-    <t>编号【KEY】</t>
+    <t>编号</t>
   </si>
   <si>
     <t>物品id</t>
@@ -367,13 +367,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1269,7 +1269,7 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:18">
       <c r="A4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="3">
         <v>200001</v>
@@ -1303,7 +1303,7 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:18">
       <c r="A5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="3">
         <v>200002</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:18">
       <c r="A6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="3">
         <v>200003</v>
@@ -1371,7 +1371,7 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:18">
       <c r="A7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="3">
         <v>200004</v>
@@ -1405,7 +1405,7 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:18">
       <c r="A8" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="3">
         <v>200005</v>

--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -367,7 +367,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -378,6 +377,7 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
